--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128941843</v>
+        <v>128938876</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464038</v>
+        <v>464248</v>
       </c>
       <c r="R2" t="n">
-        <v>6766260</v>
+        <v>6766327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +785,7 @@
         <v>128942912</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128943092</v>
+        <v>128941843</v>
       </c>
       <c r="B4" t="n">
-        <v>97503</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R4" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128938876</v>
+        <v>128943092</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464248</v>
+        <v>464160</v>
       </c>
       <c r="R5" t="n">
-        <v>6766327</v>
+        <v>6766318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,45 +1113,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128940909</v>
+        <v>128945728</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463967</v>
+        <v>464173</v>
       </c>
       <c r="R6" t="n">
-        <v>6766215</v>
+        <v>6766364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,49 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944265</v>
+        <v>128940909</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464223</v>
+        <v>463967</v>
       </c>
       <c r="R7" t="n">
-        <v>6766344</v>
+        <v>6766215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,11 +1306,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,38 +1332,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128945728</v>
+        <v>128944265</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1376,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464173</v>
+        <v>464223</v>
       </c>
       <c r="R8" t="n">
-        <v>6766364</v>
+        <v>6766344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,6 +1417,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,7 +1451,7 @@
         <v>128942042</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128941723</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>128946886</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128943510</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1988,27 +1988,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128940037</v>
+        <v>128941935</v>
       </c>
       <c r="B14" t="n">
-        <v>58086</v>
+        <v>57717</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2019,7 +2019,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2028,13 +2028,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464137</v>
+        <v>464055</v>
       </c>
       <c r="R14" t="n">
-        <v>6766260</v>
+        <v>6766275</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128941935</v>
+        <v>128942029</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464055</v>
+        <v>464073</v>
       </c>
       <c r="R15" t="n">
-        <v>6766275</v>
+        <v>6766253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128942029</v>
+        <v>128942080</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464073</v>
+        <v>464119</v>
       </c>
       <c r="R16" t="n">
-        <v>6766253</v>
+        <v>6766285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,27 +2324,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128942080</v>
+        <v>128940037</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>58090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2364,13 +2364,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464119</v>
+        <v>464137</v>
       </c>
       <c r="R17" t="n">
-        <v>6766285</v>
+        <v>6766260</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>128940882</v>
       </c>
       <c r="B18" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2548,45 +2548,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128940607</v>
+        <v>128941707</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464067</v>
+        <v>463996</v>
       </c>
       <c r="R19" t="n">
-        <v>6766216</v>
+        <v>6766236</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128941707</v>
+        <v>128946585</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463996</v>
+        <v>464208</v>
       </c>
       <c r="R20" t="n">
-        <v>6766236</v>
+        <v>6766408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,50 +2772,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128946585</v>
+        <v>128940607</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464208</v>
+        <v>464067</v>
       </c>
       <c r="R21" t="n">
-        <v>6766408</v>
+        <v>6766216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2986,32 +2986,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128941653</v>
+        <v>128943205</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463963</v>
+        <v>464160</v>
       </c>
       <c r="R23" t="n">
-        <v>6766221</v>
+        <v>6766318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3093,32 +3093,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128943205</v>
+        <v>128941653</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464160</v>
+        <v>463963</v>
       </c>
       <c r="R24" t="n">
-        <v>6766318</v>
+        <v>6766221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,7 +3203,7 @@
         <v>128940017</v>
       </c>
       <c r="B25" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>128946766</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3428,45 +3428,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128947014</v>
+        <v>128941746</v>
       </c>
       <c r="B27" t="n">
-        <v>105695</v>
+        <v>57717</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464224</v>
+        <v>464016</v>
       </c>
       <c r="R27" t="n">
-        <v>6766359</v>
+        <v>6766255</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3535,50 +3540,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128941746</v>
+        <v>128947014</v>
       </c>
       <c r="B28" t="n">
-        <v>57713</v>
+        <v>105699</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464016</v>
+        <v>464224</v>
       </c>
       <c r="R28" t="n">
-        <v>6766255</v>
+        <v>6766359</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3650,7 +3650,7 @@
         <v>128946233</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,45 +3763,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128941712</v>
+        <v>128940341</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463996</v>
+        <v>464100</v>
       </c>
       <c r="R30" t="n">
-        <v>6766236</v>
+        <v>6766234</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,49 +3875,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128945041</v>
+        <v>128941712</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464233</v>
+        <v>463996</v>
       </c>
       <c r="R31" t="n">
-        <v>6766357</v>
+        <v>6766236</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3955,11 +3956,6 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3986,10 +3982,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128940341</v>
+        <v>128943427</v>
       </c>
       <c r="B32" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3997,39 +3993,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464100</v>
+        <v>464146</v>
       </c>
       <c r="R32" t="n">
-        <v>6766234</v>
+        <v>6766334</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4098,45 +4089,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128943427</v>
+        <v>128945041</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464146</v>
+        <v>464233</v>
       </c>
       <c r="R33" t="n">
-        <v>6766334</v>
+        <v>6766357</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4179,6 +4174,11 @@
       <c r="AB33" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4208,7 +4208,7 @@
         <v>128941648</v>
       </c>
       <c r="B34" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128944811</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>128947076</v>
       </c>
       <c r="B36" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,32 +4545,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128941924</v>
+        <v>128940920</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464063</v>
+        <v>463951</v>
       </c>
       <c r="R37" t="n">
-        <v>6766246</v>
+        <v>6766222</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4652,45 +4652,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128940920</v>
+        <v>128944734</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>98636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463951</v>
+        <v>464237</v>
       </c>
       <c r="R38" t="n">
-        <v>6766222</v>
+        <v>6766360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,6 +4737,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,49 +4768,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128944734</v>
+        <v>128941924</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464237</v>
+        <v>464063</v>
       </c>
       <c r="R39" t="n">
-        <v>6766360</v>
+        <v>6766246</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4846,11 +4851,6 @@
           <t>11:56</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>10 tal synliga</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4872,6 +4872,1663 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128960932</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>464014</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6766293</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128964303</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79124</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>464208</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6766408</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128958576</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>464174</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6766418</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128960889</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>464004</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6766280</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128961919</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92798</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>463946</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6766237</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128960271</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>464059</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6766316</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128961560</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>463979</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6766276</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128961698</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>463946</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6766237</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128960230</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>464059</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6766316</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128958610</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57880</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>464174</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6766418</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128961160</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79743</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>463987</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6766274</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128958990</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>464174</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6766377</v>
+      </c>
+      <c r="S51" t="n">
+        <v>50</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128958240</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>464182</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6766438</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128958829</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>464208</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6766408</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128960668</v>
+      </c>
+      <c r="B54" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Täxberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>464014</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6766293</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128938876</v>
+        <v>128943092</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464248</v>
+        <v>464160</v>
       </c>
       <c r="R2" t="n">
-        <v>6766327</v>
+        <v>6766318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128942912</v>
+        <v>128938876</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464160</v>
+        <v>464248</v>
       </c>
       <c r="R3" t="n">
-        <v>6766318</v>
+        <v>6766327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128941843</v>
+        <v>128942912</v>
       </c>
       <c r="B4" t="n">
         <v>57717</v>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464038</v>
+        <v>464160</v>
       </c>
       <c r="R4" t="n">
-        <v>6766260</v>
+        <v>6766318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,45 +1001,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128943092</v>
+        <v>128941843</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R5" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,38 +1113,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128945728</v>
+        <v>128944265</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464173</v>
+        <v>464223</v>
       </c>
       <c r="R6" t="n">
-        <v>6766364</v>
+        <v>6766344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1198,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,45 +1229,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128940909</v>
+        <v>128945728</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463967</v>
+        <v>464173</v>
       </c>
       <c r="R7" t="n">
-        <v>6766215</v>
+        <v>6766364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,49 +1341,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944265</v>
+        <v>128940909</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464223</v>
+        <v>463967</v>
       </c>
       <c r="R8" t="n">
-        <v>6766344</v>
+        <v>6766215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,11 +1422,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3763,10 +3763,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128940341</v>
+        <v>128943427</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,39 +3774,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464100</v>
+        <v>464146</v>
       </c>
       <c r="R30" t="n">
-        <v>6766234</v>
+        <v>6766334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3875,45 +3870,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128941712</v>
+        <v>128940341</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463996</v>
+        <v>464100</v>
       </c>
       <c r="R31" t="n">
-        <v>6766236</v>
+        <v>6766234</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128943427</v>
+        <v>128941712</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464146</v>
+        <v>463996</v>
       </c>
       <c r="R32" t="n">
-        <v>6766334</v>
+        <v>6766236</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4545,32 +4545,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128940920</v>
+        <v>128941924</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463951</v>
+        <v>464063</v>
       </c>
       <c r="R37" t="n">
-        <v>6766222</v>
+        <v>6766246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4768,32 +4768,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128941924</v>
+        <v>128940920</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464063</v>
+        <v>463951</v>
       </c>
       <c r="R39" t="n">
-        <v>6766246</v>
+        <v>6766222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128961698</v>
+        <v>128960230</v>
       </c>
       <c r="B47" t="n">
         <v>8450</v>
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463946</v>
+        <v>464059</v>
       </c>
       <c r="R47" t="n">
-        <v>6766237</v>
+        <v>6766316</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128960230</v>
+        <v>128961698</v>
       </c>
       <c r="B48" t="n">
         <v>8450</v>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464059</v>
+        <v>463946</v>
       </c>
       <c r="R48" t="n">
-        <v>6766316</v>
+        <v>6766237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128943092</v>
+        <v>128938876</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464160</v>
+        <v>464248</v>
       </c>
       <c r="R2" t="n">
-        <v>6766318</v>
+        <v>6766327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128938876</v>
+        <v>128942912</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464248</v>
+        <v>464160</v>
       </c>
       <c r="R3" t="n">
-        <v>6766327</v>
+        <v>6766318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128942912</v>
+        <v>128941843</v>
       </c>
       <c r="B4" t="n">
         <v>57717</v>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R4" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128941843</v>
+        <v>128943092</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>97507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464038</v>
+        <v>464160</v>
       </c>
       <c r="R5" t="n">
-        <v>6766260</v>
+        <v>6766318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,37 +1113,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128944265</v>
+        <v>128945728</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1152,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464223</v>
+        <v>464173</v>
       </c>
       <c r="R6" t="n">
-        <v>6766344</v>
+        <v>6766364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,11 +1199,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,50 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128945728</v>
+        <v>128940909</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464173</v>
+        <v>463967</v>
       </c>
       <c r="R7" t="n">
-        <v>6766364</v>
+        <v>6766215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,45 +1332,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128940909</v>
+        <v>128944265</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463967</v>
+        <v>464223</v>
       </c>
       <c r="R8" t="n">
-        <v>6766215</v>
+        <v>6766344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,6 +1417,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2436,50 +2436,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128940882</v>
+        <v>128940607</v>
       </c>
       <c r="B18" t="n">
-        <v>57717</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463938</v>
+        <v>464067</v>
       </c>
       <c r="R18" t="n">
-        <v>6766194</v>
+        <v>6766216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,7 +2543,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128941707</v>
+        <v>128946585</v>
       </c>
       <c r="B19" t="n">
         <v>57717</v>
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463996</v>
+        <v>464208</v>
       </c>
       <c r="R19" t="n">
-        <v>6766236</v>
+        <v>6766408</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2660,7 +2655,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128946585</v>
+        <v>128940882</v>
       </c>
       <c r="B20" t="n">
         <v>57717</v>
@@ -2700,10 +2695,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464208</v>
+        <v>463938</v>
       </c>
       <c r="R20" t="n">
-        <v>6766408</v>
+        <v>6766194</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,45 +2767,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128940607</v>
+        <v>128941707</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57717</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464067</v>
+        <v>463996</v>
       </c>
       <c r="R21" t="n">
-        <v>6766216</v>
+        <v>6766236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128943427</v>
+        <v>128940341</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,34 +3774,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464146</v>
+        <v>464100</v>
       </c>
       <c r="R30" t="n">
-        <v>6766334</v>
+        <v>6766234</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,10 +3875,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128940341</v>
+        <v>128943427</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3881,39 +3886,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464100</v>
+        <v>464146</v>
       </c>
       <c r="R31" t="n">
-        <v>6766234</v>
+        <v>6766334</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128938876</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,40 +782,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128942912</v>
+        <v>128943092</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128941843</v>
+        <v>128942912</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464038</v>
+        <v>464160</v>
       </c>
       <c r="R4" t="n">
-        <v>6766260</v>
+        <v>6766318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,45 +1001,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128943092</v>
+        <v>128941843</v>
       </c>
       <c r="B5" t="n">
-        <v>97507</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R5" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1116,7 @@
         <v>128945728</v>
       </c>
       <c r="B6" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>128944265</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>128942042</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128941723</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>128946886</v>
       </c>
       <c r="B11" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>128943510</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>128941935</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>128942029</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>128942080</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128940037</v>
       </c>
       <c r="B17" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,45 +2436,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128940607</v>
+        <v>128940882</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464067</v>
+        <v>463938</v>
       </c>
       <c r="R18" t="n">
-        <v>6766216</v>
+        <v>6766194</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128946585</v>
+        <v>128941707</v>
       </c>
       <c r="B19" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,10 +2588,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464208</v>
+        <v>463996</v>
       </c>
       <c r="R19" t="n">
-        <v>6766408</v>
+        <v>6766236</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128940882</v>
+        <v>128946585</v>
       </c>
       <c r="B20" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463938</v>
+        <v>464208</v>
       </c>
       <c r="R20" t="n">
-        <v>6766194</v>
+        <v>6766408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,50 +2772,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128941707</v>
+        <v>128940607</v>
       </c>
       <c r="B21" t="n">
-        <v>57717</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463996</v>
+        <v>464067</v>
       </c>
       <c r="R21" t="n">
-        <v>6766236</v>
+        <v>6766216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2989,7 +2989,7 @@
         <v>128943205</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128940017</v>
       </c>
       <c r="B25" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>128946766</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>128941746</v>
       </c>
       <c r="B27" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>128947014</v>
       </c>
       <c r="B28" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>128946233</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128940341</v>
+        <v>128943427</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,39 +3774,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464100</v>
+        <v>464146</v>
       </c>
       <c r="R30" t="n">
-        <v>6766234</v>
+        <v>6766334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3875,10 +3870,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128943427</v>
+        <v>128940341</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3886,34 +3881,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464146</v>
+        <v>464100</v>
       </c>
       <c r="R31" t="n">
-        <v>6766334</v>
+        <v>6766234</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3982,45 +3982,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128941712</v>
+        <v>128945041</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463996</v>
+        <v>464233</v>
       </c>
       <c r="R32" t="n">
-        <v>6766236</v>
+        <v>6766357</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4063,6 +4067,11 @@
       <c r="AB32" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4089,49 +4098,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128945041</v>
+        <v>128941712</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464233</v>
+        <v>463996</v>
       </c>
       <c r="R33" t="n">
-        <v>6766357</v>
+        <v>6766236</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,11 +4179,6 @@
       <c r="AB33" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4205,38 +4205,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128941648</v>
+        <v>128944811</v>
       </c>
       <c r="B34" t="n">
-        <v>57717</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4245,10 +4244,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463963</v>
+        <v>464229</v>
       </c>
       <c r="R34" t="n">
-        <v>6766221</v>
+        <v>6766349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4291,6 +4290,11 @@
       <c r="AB34" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 40 synliga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4317,37 +4321,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128944811</v>
+        <v>128941648</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4356,10 +4361,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464229</v>
+        <v>463963</v>
       </c>
       <c r="R35" t="n">
-        <v>6766349</v>
+        <v>6766221</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,11 +4407,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ca 40 synliga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4436,7 +4436,7 @@
         <v>128947076</v>
       </c>
       <c r="B36" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>128941924</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4652,49 +4652,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128944734</v>
+        <v>128940920</v>
       </c>
       <c r="B38" t="n">
-        <v>98636</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464237</v>
+        <v>463951</v>
       </c>
       <c r="R38" t="n">
-        <v>6766360</v>
+        <v>6766222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,11 +4733,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4768,45 +4759,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128940920</v>
+        <v>128944734</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463951</v>
+        <v>464237</v>
       </c>
       <c r="R39" t="n">
-        <v>6766222</v>
+        <v>6766360</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4849,6 +4844,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4878,7 +4878,7 @@
         <v>128960932</v>
       </c>
       <c r="B40" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>128964303</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>128958576</v>
       </c>
       <c r="B42" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>128960889</v>
       </c>
       <c r="B43" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128961919</v>
       </c>
       <c r="B44" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>128960271</v>
       </c>
       <c r="B45" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>128961560</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>128958610</v>
       </c>
       <c r="B49" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>128961160</v>
       </c>
       <c r="B50" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>128958990</v>
       </c>
       <c r="B51" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6206,50 +6206,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128958240</v>
+        <v>128958829</v>
       </c>
       <c r="B52" t="n">
-        <v>57717</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464182</v>
+        <v>464208</v>
       </c>
       <c r="R52" t="n">
-        <v>6766438</v>
+        <v>6766408</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,45 +6313,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128958829</v>
+        <v>128958240</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464208</v>
+        <v>464182</v>
       </c>
       <c r="R53" t="n">
-        <v>6766408</v>
+        <v>6766438</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -1113,45 +1113,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128940909</v>
+        <v>128944265</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>98651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463967</v>
+        <v>464223</v>
       </c>
       <c r="R6" t="n">
-        <v>6766215</v>
+        <v>6766344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1198,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,37 +1229,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944265</v>
+        <v>128945728</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1259,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464223</v>
+        <v>464173</v>
       </c>
       <c r="R7" t="n">
-        <v>6766344</v>
+        <v>6766364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,11 +1315,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,50 +1341,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128945728</v>
+        <v>128940909</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464173</v>
+        <v>463967</v>
       </c>
       <c r="R8" t="n">
-        <v>6766364</v>
+        <v>6766215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128946886</v>
+        <v>128943510</v>
       </c>
       <c r="B11" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,34 +1673,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464227</v>
+        <v>464146</v>
       </c>
       <c r="R11" t="n">
-        <v>6766364</v>
+        <v>6766334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,10 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128943510</v>
+        <v>128946886</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,39 +1785,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464146</v>
+        <v>464227</v>
       </c>
       <c r="R12" t="n">
-        <v>6766334</v>
+        <v>6766364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1988,27 +1988,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128940037</v>
+        <v>128941935</v>
       </c>
       <c r="B14" t="n">
-        <v>58093</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2019,7 +2019,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2028,13 +2028,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464137</v>
+        <v>464055</v>
       </c>
       <c r="R14" t="n">
-        <v>6766260</v>
+        <v>6766275</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128941935</v>
+        <v>128942029</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464055</v>
+        <v>464073</v>
       </c>
       <c r="R15" t="n">
-        <v>6766275</v>
+        <v>6766253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128942029</v>
+        <v>128942080</v>
       </c>
       <c r="B16" t="n">
         <v>57720</v>
@@ -2243,7 +2243,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464073</v>
+        <v>464119</v>
       </c>
       <c r="R16" t="n">
-        <v>6766253</v>
+        <v>6766285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,27 +2324,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128942080</v>
+        <v>128940037</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2364,13 +2364,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464119</v>
+        <v>464137</v>
       </c>
       <c r="R17" t="n">
-        <v>6766285</v>
+        <v>6766260</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4545,32 +4545,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128940920</v>
+        <v>128941924</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463951</v>
+        <v>464063</v>
       </c>
       <c r="R37" t="n">
-        <v>6766222</v>
+        <v>6766246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4652,49 +4652,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128944734</v>
+        <v>128940920</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464237</v>
+        <v>463951</v>
       </c>
       <c r="R38" t="n">
-        <v>6766360</v>
+        <v>6766222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,11 +4733,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4768,45 +4759,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128941924</v>
+        <v>128944734</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>98651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464063</v>
+        <v>464237</v>
       </c>
       <c r="R39" t="n">
-        <v>6766246</v>
+        <v>6766360</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4849,6 +4844,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6206,50 +6206,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128958240</v>
+        <v>128958829</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464182</v>
+        <v>464208</v>
       </c>
       <c r="R52" t="n">
-        <v>6766438</v>
+        <v>6766408</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,45 +6313,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128958829</v>
+        <v>128958240</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464208</v>
+        <v>464182</v>
       </c>
       <c r="R53" t="n">
-        <v>6766408</v>
+        <v>6766438</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -782,35 +782,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128943092</v>
+        <v>128942912</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128942912</v>
+        <v>128941843</v>
       </c>
       <c r="B4" t="n">
         <v>57720</v>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R4" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128941843</v>
+        <v>128943092</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>97527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464038</v>
+        <v>464160</v>
       </c>
       <c r="R5" t="n">
-        <v>6766260</v>
+        <v>6766318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,37 +1113,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128944265</v>
+        <v>128945728</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1152,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464223</v>
+        <v>464173</v>
       </c>
       <c r="R6" t="n">
-        <v>6766344</v>
+        <v>6766364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,11 +1199,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,50 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128945728</v>
+        <v>128940909</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464173</v>
+        <v>463967</v>
       </c>
       <c r="R7" t="n">
-        <v>6766364</v>
+        <v>6766215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,45 +1332,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128940909</v>
+        <v>128944265</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463967</v>
+        <v>464223</v>
       </c>
       <c r="R8" t="n">
-        <v>6766215</v>
+        <v>6766344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,6 +1417,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1662,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128943510</v>
+        <v>128946886</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,39 +1673,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464146</v>
+        <v>464227</v>
       </c>
       <c r="R11" t="n">
-        <v>6766334</v>
+        <v>6766364</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128946886</v>
+        <v>128943510</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,34 +1780,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464227</v>
+        <v>464146</v>
       </c>
       <c r="R12" t="n">
-        <v>6766364</v>
+        <v>6766334</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128941935</v>
+        <v>128942029</v>
       </c>
       <c r="B14" t="n">
         <v>57720</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464055</v>
+        <v>464073</v>
       </c>
       <c r="R14" t="n">
-        <v>6766275</v>
+        <v>6766253</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128942029</v>
+        <v>128941935</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464073</v>
+        <v>464055</v>
       </c>
       <c r="R15" t="n">
-        <v>6766253</v>
+        <v>6766275</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2986,32 +2986,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128943205</v>
+        <v>128941653</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464160</v>
+        <v>463963</v>
       </c>
       <c r="R23" t="n">
-        <v>6766318</v>
+        <v>6766221</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3093,32 +3093,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128941653</v>
+        <v>128943205</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463963</v>
+        <v>464160</v>
       </c>
       <c r="R24" t="n">
-        <v>6766221</v>
+        <v>6766318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3315,7 +3315,7 @@
         <v>128946766</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>128947014</v>
       </c>
       <c r="B28" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>128946233</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128940341</v>
+        <v>128943427</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,39 +3774,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464100</v>
+        <v>464146</v>
       </c>
       <c r="R30" t="n">
-        <v>6766234</v>
+        <v>6766334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3875,10 +3870,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128943427</v>
+        <v>128940341</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3886,34 +3881,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464146</v>
+        <v>464100</v>
       </c>
       <c r="R31" t="n">
-        <v>6766334</v>
+        <v>6766234</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4092,7 +4092,7 @@
         <v>128945041</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128944811</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4545,32 +4545,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128941924</v>
+        <v>128940920</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464063</v>
+        <v>463951</v>
       </c>
       <c r="R37" t="n">
-        <v>6766246</v>
+        <v>6766222</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4652,45 +4652,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128940920</v>
+        <v>128944734</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>98656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463951</v>
+        <v>464237</v>
       </c>
       <c r="R38" t="n">
-        <v>6766222</v>
+        <v>6766360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,6 +4737,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,49 +4768,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128944734</v>
+        <v>128941924</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464237</v>
+        <v>464063</v>
       </c>
       <c r="R39" t="n">
-        <v>6766360</v>
+        <v>6766246</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4844,11 +4849,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5325,7 +5325,7 @@
         <v>128961919</v>
       </c>
       <c r="B44" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6206,45 +6206,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128958829</v>
+        <v>128958240</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464208</v>
+        <v>464182</v>
       </c>
       <c r="R52" t="n">
-        <v>6766408</v>
+        <v>6766438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6313,50 +6318,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128958240</v>
+        <v>128958829</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464182</v>
+        <v>464208</v>
       </c>
       <c r="R53" t="n">
-        <v>6766438</v>
+        <v>6766408</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128938876</v>
+        <v>128942912</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464248</v>
+        <v>464160</v>
       </c>
       <c r="R2" t="n">
-        <v>6766327</v>
+        <v>6766318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128942912</v>
+        <v>128941843</v>
       </c>
       <c r="B3" t="n">
         <v>57720</v>
@@ -822,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R3" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128941843</v>
+        <v>128943092</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>97530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464038</v>
+        <v>464160</v>
       </c>
       <c r="R4" t="n">
-        <v>6766260</v>
+        <v>6766318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128943092</v>
+        <v>128938876</v>
       </c>
       <c r="B5" t="n">
-        <v>97527</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464160</v>
+        <v>464248</v>
       </c>
       <c r="R5" t="n">
-        <v>6766318</v>
+        <v>6766327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
         <v>128944265</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>128942042</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128941723</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128946886</v>
+        <v>128943510</v>
       </c>
       <c r="B11" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,34 +1673,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464227</v>
+        <v>464146</v>
       </c>
       <c r="R11" t="n">
-        <v>6766364</v>
+        <v>6766334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,10 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128943510</v>
+        <v>128946886</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,39 +1785,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464146</v>
+        <v>464227</v>
       </c>
       <c r="R12" t="n">
-        <v>6766334</v>
+        <v>6766364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128941935</v>
+        <v>128942080</v>
       </c>
       <c r="B15" t="n">
         <v>57720</v>
@@ -2131,7 +2131,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464055</v>
+        <v>464119</v>
       </c>
       <c r="R15" t="n">
-        <v>6766275</v>
+        <v>6766285</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128942080</v>
+        <v>128941935</v>
       </c>
       <c r="B16" t="n">
         <v>57720</v>
@@ -2243,7 +2243,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464119</v>
+        <v>464055</v>
       </c>
       <c r="R16" t="n">
-        <v>6766285</v>
+        <v>6766275</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2436,50 +2436,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128940882</v>
+        <v>128940607</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463938</v>
+        <v>464067</v>
       </c>
       <c r="R18" t="n">
-        <v>6766194</v>
+        <v>6766216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,7 +2543,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128941707</v>
+        <v>128940882</v>
       </c>
       <c r="B19" t="n">
         <v>57720</v>
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463996</v>
+        <v>463938</v>
       </c>
       <c r="R19" t="n">
-        <v>6766236</v>
+        <v>6766194</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2660,7 +2655,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128946585</v>
+        <v>128941707</v>
       </c>
       <c r="B20" t="n">
         <v>57720</v>
@@ -2700,10 +2695,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464208</v>
+        <v>463996</v>
       </c>
       <c r="R20" t="n">
-        <v>6766408</v>
+        <v>6766236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,45 +2767,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128940607</v>
+        <v>128946585</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464067</v>
+        <v>464208</v>
       </c>
       <c r="R21" t="n">
-        <v>6766216</v>
+        <v>6766408</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3096,7 +3096,7 @@
         <v>128943205</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>128946766</v>
       </c>
       <c r="B26" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>128947014</v>
       </c>
       <c r="B28" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>128946233</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3763,32 +3763,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128943427</v>
+        <v>128941712</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464146</v>
+        <v>463996</v>
       </c>
       <c r="R30" t="n">
-        <v>6766334</v>
+        <v>6766236</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,38 +3870,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128940341</v>
+        <v>128945041</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3910,10 +3909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464100</v>
+        <v>464233</v>
       </c>
       <c r="R31" t="n">
-        <v>6766234</v>
+        <v>6766357</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3956,6 +3955,11 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3982,32 +3986,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128941712</v>
+        <v>128943427</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4017,10 +4021,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463996</v>
+        <v>464146</v>
       </c>
       <c r="R32" t="n">
-        <v>6766236</v>
+        <v>6766334</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,37 +4093,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128945041</v>
+        <v>128940341</v>
       </c>
       <c r="B33" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464233</v>
+        <v>464100</v>
       </c>
       <c r="R33" t="n">
-        <v>6766357</v>
+        <v>6766234</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,11 +4179,6 @@
       <c r="AB33" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4205,38 +4205,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128941648</v>
+        <v>128944811</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4245,10 +4244,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463963</v>
+        <v>464229</v>
       </c>
       <c r="R34" t="n">
-        <v>6766221</v>
+        <v>6766349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4291,6 +4290,11 @@
       <c r="AB34" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 40 synliga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4317,37 +4321,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128944811</v>
+        <v>128941648</v>
       </c>
       <c r="B35" t="n">
-        <v>98656</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4356,10 +4361,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464229</v>
+        <v>463963</v>
       </c>
       <c r="R35" t="n">
-        <v>6766349</v>
+        <v>6766221</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4402,11 +4407,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ca 40 synliga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4545,32 +4545,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128940920</v>
+        <v>128941924</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463951</v>
+        <v>464063</v>
       </c>
       <c r="R37" t="n">
-        <v>6766222</v>
+        <v>6766246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
         <v>128944734</v>
       </c>
       <c r="B38" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,32 +4768,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128941924</v>
+        <v>128940920</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464063</v>
+        <v>463951</v>
       </c>
       <c r="R39" t="n">
-        <v>6766246</v>
+        <v>6766222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4994,7 +4994,7 @@
         <v>128964303</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128961919</v>
       </c>
       <c r="B44" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>128961160</v>
       </c>
       <c r="B50" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128942912</v>
+        <v>128938876</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464160</v>
+        <v>464248</v>
       </c>
       <c r="R2" t="n">
-        <v>6766318</v>
+        <v>6766327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128941843</v>
+        <v>128942912</v>
       </c>
       <c r="B3" t="n">
         <v>57720</v>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464038</v>
+        <v>464160</v>
       </c>
       <c r="R3" t="n">
-        <v>6766260</v>
+        <v>6766318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128943092</v>
+        <v>128941843</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R4" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128938876</v>
+        <v>128943092</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464248</v>
+        <v>464160</v>
       </c>
       <c r="R5" t="n">
-        <v>6766327</v>
+        <v>6766318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128942029</v>
+        <v>128941935</v>
       </c>
       <c r="B14" t="n">
         <v>57720</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464073</v>
+        <v>464055</v>
       </c>
       <c r="R14" t="n">
-        <v>6766253</v>
+        <v>6766275</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,27 +2100,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128942080</v>
+        <v>128940037</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2131,7 +2131,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2140,13 +2140,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464119</v>
+        <v>464137</v>
       </c>
       <c r="R15" t="n">
-        <v>6766285</v>
+        <v>6766260</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128941935</v>
+        <v>128942029</v>
       </c>
       <c r="B16" t="n">
         <v>57720</v>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464055</v>
+        <v>464073</v>
       </c>
       <c r="R16" t="n">
-        <v>6766275</v>
+        <v>6766253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,27 +2324,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128940037</v>
+        <v>128942080</v>
       </c>
       <c r="B17" t="n">
-        <v>58093</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2364,13 +2364,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464137</v>
+        <v>464119</v>
       </c>
       <c r="R17" t="n">
-        <v>6766260</v>
+        <v>6766285</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,45 +2436,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128940607</v>
+        <v>128940882</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464067</v>
+        <v>463938</v>
       </c>
       <c r="R18" t="n">
-        <v>6766216</v>
+        <v>6766194</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,7 +2548,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128940882</v>
+        <v>128941707</v>
       </c>
       <c r="B19" t="n">
         <v>57720</v>
@@ -2583,10 +2588,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463938</v>
+        <v>463996</v>
       </c>
       <c r="R19" t="n">
-        <v>6766194</v>
+        <v>6766236</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,7 +2660,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128941707</v>
+        <v>128946585</v>
       </c>
       <c r="B20" t="n">
         <v>57720</v>
@@ -2695,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463996</v>
+        <v>464208</v>
       </c>
       <c r="R20" t="n">
-        <v>6766236</v>
+        <v>6766408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,50 +2772,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128946585</v>
+        <v>128940607</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464208</v>
+        <v>464067</v>
       </c>
       <c r="R21" t="n">
-        <v>6766408</v>
+        <v>6766216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3428,50 +3428,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128941746</v>
+        <v>128947014</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>105722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464016</v>
+        <v>464224</v>
       </c>
       <c r="R27" t="n">
-        <v>6766255</v>
+        <v>6766359</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3540,45 +3535,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128947014</v>
+        <v>128941746</v>
       </c>
       <c r="B28" t="n">
-        <v>105722</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464224</v>
+        <v>464016</v>
       </c>
       <c r="R28" t="n">
-        <v>6766359</v>
+        <v>6766255</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3763,32 +3763,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128941712</v>
+        <v>128943427</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463996</v>
+        <v>464146</v>
       </c>
       <c r="R30" t="n">
-        <v>6766236</v>
+        <v>6766334</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,49 +3870,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128945041</v>
+        <v>128941712</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464233</v>
+        <v>463996</v>
       </c>
       <c r="R31" t="n">
-        <v>6766357</v>
+        <v>6766236</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3955,11 +3951,6 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3986,45 +3977,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128943427</v>
+        <v>128945041</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464146</v>
+        <v>464233</v>
       </c>
       <c r="R32" t="n">
-        <v>6766334</v>
+        <v>6766357</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,6 +4062,11 @@
       <c r="AB32" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,37 +4205,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128944811</v>
+        <v>128941648</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4244,10 +4245,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464229</v>
+        <v>463963</v>
       </c>
       <c r="R34" t="n">
-        <v>6766349</v>
+        <v>6766221</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4290,11 +4291,6 @@
       <c r="AB34" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 40 synliga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4321,38 +4317,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128941648</v>
+        <v>128944811</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4361,10 +4356,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463963</v>
+        <v>464229</v>
       </c>
       <c r="R35" t="n">
-        <v>6766221</v>
+        <v>6766349</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4407,6 +4402,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ca 40 synliga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4545,32 +4545,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128941924</v>
+        <v>128940920</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464063</v>
+        <v>463951</v>
       </c>
       <c r="R37" t="n">
-        <v>6766246</v>
+        <v>6766222</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4768,32 +4768,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128940920</v>
+        <v>128941924</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463951</v>
+        <v>464063</v>
       </c>
       <c r="R39" t="n">
-        <v>6766222</v>
+        <v>6766246</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5322,37 +5322,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128961919</v>
+        <v>128960271</v>
       </c>
       <c r="B44" t="n">
-        <v>92819</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5361,10 +5362,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>463946</v>
+        <v>464059</v>
       </c>
       <c r="R44" t="n">
-        <v>6766237</v>
+        <v>6766316</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5433,38 +5434,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128960271</v>
+        <v>128961919</v>
       </c>
       <c r="B45" t="n">
-        <v>57720</v>
+        <v>92819</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464059</v>
+        <v>463946</v>
       </c>
       <c r="R45" t="n">
-        <v>6766316</v>
+        <v>6766237</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6206,50 +6206,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128958240</v>
+        <v>128958829</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464182</v>
+        <v>464208</v>
       </c>
       <c r="R52" t="n">
-        <v>6766438</v>
+        <v>6766408</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,45 +6313,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128958829</v>
+        <v>128958240</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464208</v>
+        <v>464182</v>
       </c>
       <c r="R53" t="n">
-        <v>6766408</v>
+        <v>6766438</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -782,40 +782,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128942912</v>
+        <v>128943092</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128941843</v>
+        <v>128942912</v>
       </c>
       <c r="B4" t="n">
         <v>57720</v>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464038</v>
+        <v>464160</v>
       </c>
       <c r="R4" t="n">
-        <v>6766260</v>
+        <v>6766318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,45 +1001,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128943092</v>
+        <v>128941843</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R5" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,50 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128945728</v>
+        <v>128940909</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464173</v>
+        <v>463967</v>
       </c>
       <c r="R6" t="n">
-        <v>6766364</v>
+        <v>6766215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,45 +1220,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128940909</v>
+        <v>128945728</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463967</v>
+        <v>464173</v>
       </c>
       <c r="R7" t="n">
-        <v>6766215</v>
+        <v>6766364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2100,27 +2100,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128940037</v>
+        <v>128942029</v>
       </c>
       <c r="B15" t="n">
-        <v>58093</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2131,7 +2131,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2140,13 +2140,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464137</v>
+        <v>464073</v>
       </c>
       <c r="R15" t="n">
-        <v>6766260</v>
+        <v>6766253</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128942029</v>
+        <v>128942080</v>
       </c>
       <c r="B16" t="n">
         <v>57720</v>
@@ -2243,7 +2243,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464073</v>
+        <v>464119</v>
       </c>
       <c r="R16" t="n">
-        <v>6766253</v>
+        <v>6766285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,27 +2324,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128942080</v>
+        <v>128940037</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>58093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2364,13 +2364,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464119</v>
+        <v>464137</v>
       </c>
       <c r="R17" t="n">
-        <v>6766285</v>
+        <v>6766260</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2986,32 +2986,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128941653</v>
+        <v>128943205</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463963</v>
+        <v>464160</v>
       </c>
       <c r="R23" t="n">
-        <v>6766221</v>
+        <v>6766318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3093,32 +3093,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128943205</v>
+        <v>128941653</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464160</v>
+        <v>463963</v>
       </c>
       <c r="R24" t="n">
-        <v>6766318</v>
+        <v>6766221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4545,45 +4545,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128940920</v>
+        <v>128944734</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463951</v>
+        <v>464237</v>
       </c>
       <c r="R37" t="n">
-        <v>6766222</v>
+        <v>6766360</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,6 +4630,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4652,49 +4661,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128944734</v>
+        <v>128941924</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464237</v>
+        <v>464063</v>
       </c>
       <c r="R38" t="n">
-        <v>6766360</v>
+        <v>6766246</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,11 +4742,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4768,32 +4768,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128941924</v>
+        <v>128940920</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464063</v>
+        <v>463951</v>
       </c>
       <c r="R39" t="n">
-        <v>6766246</v>
+        <v>6766222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6206,45 +6206,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128958829</v>
+        <v>128958240</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464208</v>
+        <v>464182</v>
       </c>
       <c r="R52" t="n">
-        <v>6766408</v>
+        <v>6766438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6313,50 +6318,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128958240</v>
+        <v>128958829</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464182</v>
+        <v>464208</v>
       </c>
       <c r="R53" t="n">
-        <v>6766438</v>
+        <v>6766408</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128938876</v>
+        <v>128943092</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464248</v>
+        <v>464160</v>
       </c>
       <c r="R2" t="n">
-        <v>6766327</v>
+        <v>6766318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,35 +782,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128943092</v>
+        <v>128942912</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128942912</v>
+        <v>128941843</v>
       </c>
       <c r="B4" t="n">
         <v>57720</v>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R4" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128941843</v>
+        <v>128938876</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464038</v>
+        <v>464248</v>
       </c>
       <c r="R5" t="n">
-        <v>6766260</v>
+        <v>6766327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1220,38 +1220,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128945728</v>
+        <v>128944265</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464173</v>
+        <v>464223</v>
       </c>
       <c r="R7" t="n">
-        <v>6766364</v>
+        <v>6766344</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1305,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,37 +1336,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944265</v>
+        <v>128945728</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1371,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464223</v>
+        <v>464173</v>
       </c>
       <c r="R8" t="n">
-        <v>6766344</v>
+        <v>6766364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,11 +1422,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2436,50 +2436,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128940882</v>
+        <v>128940607</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463938</v>
+        <v>464067</v>
       </c>
       <c r="R18" t="n">
-        <v>6766194</v>
+        <v>6766216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,7 +2543,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128941707</v>
+        <v>128940882</v>
       </c>
       <c r="B19" t="n">
         <v>57720</v>
@@ -2588,10 +2583,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463996</v>
+        <v>463938</v>
       </c>
       <c r="R19" t="n">
-        <v>6766236</v>
+        <v>6766194</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2660,7 +2655,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128946585</v>
+        <v>128941707</v>
       </c>
       <c r="B20" t="n">
         <v>57720</v>
@@ -2700,10 +2695,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464208</v>
+        <v>463996</v>
       </c>
       <c r="R20" t="n">
-        <v>6766408</v>
+        <v>6766236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,45 +2767,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128940607</v>
+        <v>128946585</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464067</v>
+        <v>464208</v>
       </c>
       <c r="R21" t="n">
-        <v>6766216</v>
+        <v>6766408</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3428,45 +3428,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128947014</v>
+        <v>128941746</v>
       </c>
       <c r="B27" t="n">
-        <v>105722</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464224</v>
+        <v>464016</v>
       </c>
       <c r="R27" t="n">
-        <v>6766359</v>
+        <v>6766255</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3535,50 +3540,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128941746</v>
+        <v>128947014</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>105722</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464016</v>
+        <v>464224</v>
       </c>
       <c r="R28" t="n">
-        <v>6766255</v>
+        <v>6766359</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3870,45 +3870,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128941712</v>
+        <v>128940341</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463996</v>
+        <v>464100</v>
       </c>
       <c r="R31" t="n">
-        <v>6766236</v>
+        <v>6766234</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4093,50 +4098,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128940341</v>
+        <v>128941712</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464100</v>
+        <v>463996</v>
       </c>
       <c r="R33" t="n">
-        <v>6766234</v>
+        <v>6766236</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4545,49 +4545,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128944734</v>
+        <v>128941924</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464237</v>
+        <v>464063</v>
       </c>
       <c r="R37" t="n">
-        <v>6766360</v>
+        <v>6766246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,11 +4626,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4661,32 +4652,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128941924</v>
+        <v>128940920</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4696,10 +4687,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464063</v>
+        <v>463951</v>
       </c>
       <c r="R38" t="n">
-        <v>6766246</v>
+        <v>6766222</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4768,45 +4759,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128940920</v>
+        <v>128944734</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463951</v>
+        <v>464237</v>
       </c>
       <c r="R39" t="n">
-        <v>6766222</v>
+        <v>6766360</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4849,6 +4844,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5322,38 +5322,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128960271</v>
+        <v>128961919</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>92819</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5362,10 +5361,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464059</v>
+        <v>463946</v>
       </c>
       <c r="R44" t="n">
-        <v>6766316</v>
+        <v>6766237</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5434,37 +5433,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128961919</v>
+        <v>128960271</v>
       </c>
       <c r="B45" t="n">
-        <v>92819</v>
+        <v>57720</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>463946</v>
+        <v>464059</v>
       </c>
       <c r="R45" t="n">
-        <v>6766237</v>
+        <v>6766316</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6206,50 +6206,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128958240</v>
+        <v>128958829</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464182</v>
+        <v>464208</v>
       </c>
       <c r="R52" t="n">
-        <v>6766438</v>
+        <v>6766408</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,45 +6313,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128958829</v>
+        <v>128958240</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464208</v>
+        <v>464182</v>
       </c>
       <c r="R53" t="n">
-        <v>6766408</v>
+        <v>6766438</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 41410-2025 artfynd.xlsx
+++ b/artfynd/A 41410-2025 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128943092</v>
+        <v>128941843</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464160</v>
+        <v>464038</v>
       </c>
       <c r="R2" t="n">
-        <v>6766318</v>
+        <v>6766260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128942912</v>
+        <v>128938876</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464160</v>
+        <v>464248</v>
       </c>
       <c r="R3" t="n">
-        <v>6766318</v>
+        <v>6766327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128941843</v>
+        <v>128943092</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464038</v>
+        <v>464160</v>
       </c>
       <c r="R4" t="n">
-        <v>6766260</v>
+        <v>6766318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128938876</v>
+        <v>128942912</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +1012,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464248</v>
+        <v>464160</v>
       </c>
       <c r="R5" t="n">
-        <v>6766327</v>
+        <v>6766318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,45 +1113,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128940909</v>
+        <v>128945728</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463967</v>
+        <v>464173</v>
       </c>
       <c r="R6" t="n">
-        <v>6766215</v>
+        <v>6766364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,49 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944265</v>
+        <v>128940909</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464223</v>
+        <v>463967</v>
       </c>
       <c r="R7" t="n">
-        <v>6766344</v>
+        <v>6766215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,11 +1306,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,38 +1332,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128945728</v>
+        <v>128944265</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1376,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464173</v>
+        <v>464223</v>
       </c>
       <c r="R8" t="n">
-        <v>6766364</v>
+        <v>6766344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,6 +1417,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50 tal synliga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,7 +1451,7 @@
         <v>128942042</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>128941723</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,50 +1662,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128943510</v>
+        <v>128941913</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464146</v>
+        <v>464052</v>
       </c>
       <c r="R11" t="n">
-        <v>6766334</v>
+        <v>6766230</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128946886</v>
+        <v>128943510</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,34 +1780,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464227</v>
+        <v>464146</v>
       </c>
       <c r="R12" t="n">
-        <v>6766364</v>
+        <v>6766334</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,32 +1881,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128941913</v>
+        <v>128946886</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464052</v>
+        <v>464227</v>
       </c>
       <c r="R13" t="n">
-        <v>6766230</v>
+        <v>6766364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
         <v>128941935</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>128942029</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,27 +2212,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128942080</v>
+        <v>128940037</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>58095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464119</v>
+        <v>464137</v>
       </c>
       <c r="R16" t="n">
-        <v>6766285</v>
+        <v>6766260</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,27 +2324,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128940037</v>
+        <v>128942080</v>
       </c>
       <c r="B17" t="n">
-        <v>58093</v>
+        <v>57722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2355,7 +2355,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2364,13 +2364,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464137</v>
+        <v>464119</v>
       </c>
       <c r="R17" t="n">
-        <v>6766260</v>
+        <v>6766285</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,45 +2436,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128940607</v>
+        <v>128940882</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464067</v>
+        <v>463938</v>
       </c>
       <c r="R18" t="n">
-        <v>6766216</v>
+        <v>6766194</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128940882</v>
+        <v>128941707</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,10 +2588,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463938</v>
+        <v>463996</v>
       </c>
       <c r="R19" t="n">
-        <v>6766194</v>
+        <v>6766236</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128941707</v>
+        <v>128946585</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463996</v>
+        <v>464208</v>
       </c>
       <c r="R20" t="n">
-        <v>6766236</v>
+        <v>6766408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,50 +2772,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128946585</v>
+        <v>128940607</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464208</v>
+        <v>464067</v>
       </c>
       <c r="R21" t="n">
-        <v>6766408</v>
+        <v>6766216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2989,7 +2989,7 @@
         <v>128943205</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>128940017</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>128946766</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3428,50 +3428,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128941746</v>
+        <v>128947014</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>105732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464016</v>
+        <v>464224</v>
       </c>
       <c r="R27" t="n">
-        <v>6766255</v>
+        <v>6766359</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3540,45 +3535,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128947014</v>
+        <v>128941746</v>
       </c>
       <c r="B28" t="n">
-        <v>105722</v>
+        <v>57722</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464224</v>
+        <v>464016</v>
       </c>
       <c r="R28" t="n">
-        <v>6766359</v>
+        <v>6766255</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3650,7 +3650,7 @@
         <v>128946233</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>128943427</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>128940341</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,49 +3982,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128945041</v>
+        <v>128941712</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464233</v>
+        <v>463996</v>
       </c>
       <c r="R32" t="n">
-        <v>6766357</v>
+        <v>6766236</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,11 +4063,6 @@
       <c r="AB32" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4098,45 +4089,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128941712</v>
+        <v>128945041</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>98669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463996</v>
+        <v>464233</v>
       </c>
       <c r="R33" t="n">
-        <v>6766236</v>
+        <v>6766357</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4179,6 +4174,11 @@
       <c r="AB33" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 50 synliga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4208,7 +4208,7 @@
         <v>128941648</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128944811</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>128947076</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>128941924</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4652,45 +4652,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128940920</v>
+        <v>128944734</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>98669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463951</v>
+        <v>464237</v>
       </c>
       <c r="R38" t="n">
-        <v>6766222</v>
+        <v>6766360</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4733,6 +4737,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4759,49 +4768,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128944734</v>
+        <v>128940920</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464237</v>
+        <v>463951</v>
       </c>
       <c r="R39" t="n">
-        <v>6766360</v>
+        <v>6766222</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4844,11 +4849,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>10 tal synliga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4878,7 +4878,7 @@
         <v>128960932</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>128964303</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>128958576</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>128960889</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>128961919</v>
       </c>
       <c r="B44" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>128960271</v>
       </c>
       <c r="B45" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>128961560</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>128958610</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>128961160</v>
       </c>
       <c r="B50" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>128958990</v>
       </c>
       <c r="B51" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6206,45 +6206,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128958829</v>
+        <v>128958240</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464208</v>
+        <v>464182</v>
       </c>
       <c r="R52" t="n">
-        <v>6766408</v>
+        <v>6766438</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6313,50 +6318,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128958240</v>
+        <v>128958829</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Täxberget, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464182</v>
+        <v>464208</v>
       </c>
       <c r="R53" t="n">
-        <v>6766438</v>
+        <v>6766408</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
